--- a/data/trans_camb/P37-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P37-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,74</t>
+          <t>-3,72; 8,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 5,74</t>
+          <t>-6,5; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,05</t>
+          <t>6,46; 20,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 10,96</t>
+          <t>-1,83; 10,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 10,75</t>
+          <t>-1,82; 10,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 30,51</t>
+          <t>18,21; 30,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 7,25</t>
+          <t>-0,97; 8,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 6,23</t>
+          <t>-2,31; 6,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,72; 23,18</t>
+          <t>14,21; 23,22</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 71,94</t>
+          <t>-21,62; 70,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 47,87</t>
+          <t>-36,06; 51,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,43; 182,92</t>
+          <t>34,23; 171,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 115,61</t>
+          <t>-13,56; 113,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 118,3</t>
+          <t>-14,08; 113,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>112,67; 336,04</t>
+          <t>115,63; 341,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 64,18</t>
+          <t>-7,06; 73,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 54,51</t>
+          <t>-14,97; 58,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,81; 209,62</t>
+          <t>88,59; 204,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,27</t>
+          <t>3,01; 12,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,05</t>
+          <t>1,28; 10,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,45; 22,16</t>
+          <t>11,46; 22,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,11</t>
+          <t>0,42; 9,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,98</t>
+          <t>-3,53; 5,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 23,33</t>
+          <t>14,43; 23,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,58</t>
+          <t>2,58; 9,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 6,25</t>
+          <t>-0,1; 6,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 21,36</t>
+          <t>14,11; 21,39</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,92; 143,1</t>
+          <t>22,35; 143,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 120,56</t>
+          <t>9,72; 123,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,46; 259,71</t>
+          <t>87,47; 262,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 87,66</t>
+          <t>2,53; 92,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 47,75</t>
+          <t>-24,22; 48,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,44; 226,42</t>
+          <t>100,29; 231,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,84; 96,83</t>
+          <t>20,11; 95,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 61,57</t>
+          <t>-0,64; 63,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107,36; 216,67</t>
+          <t>107,64; 217,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 12,03</t>
+          <t>-0,4; 11,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,24</t>
+          <t>-2,07; 9,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 17,72</t>
+          <t>6,32; 17,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 5,98</t>
+          <t>-6,51; 5,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 8,92</t>
+          <t>-3,56; 9,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,73; 17,98</t>
+          <t>5,67; 17,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,98</t>
+          <t>-1,7; 6,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 7,46</t>
+          <t>-1,07; 7,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 16,71</t>
+          <t>7,96; 16,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 96,36</t>
+          <t>-2,47; 95,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 73,94</t>
+          <t>-11,75; 84,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,61; 141,58</t>
+          <t>33,77; 142,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 37,94</t>
+          <t>-29,04; 36,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 56,98</t>
+          <t>-16,39; 57,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,73; 114,16</t>
+          <t>24,02; 112,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 47,15</t>
+          <t>-9,26; 43,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 50,66</t>
+          <t>-6,46; 50,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,82; 113,21</t>
+          <t>41,05; 106,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 11,73</t>
+          <t>0,25; 11,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 12,69</t>
+          <t>1,9; 12,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,88; 27,22</t>
+          <t>13,22; 27,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 13,2</t>
+          <t>1,28; 12,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,63</t>
+          <t>-0,98; 10,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 20,73</t>
+          <t>-0,34; 20,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 10,4</t>
+          <t>2,68; 10,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,28</t>
+          <t>1,86; 9,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,33; 21,4</t>
+          <t>6,42; 21,32</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 120,56</t>
+          <t>0,93; 114,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,33; 129,62</t>
+          <t>13,75; 132,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,7; 278,05</t>
+          <t>86,59; 268,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 96,87</t>
+          <t>5,59; 89,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 76,79</t>
+          <t>-5,09; 73,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 136,57</t>
+          <t>0,42; 140,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,98; 84,42</t>
+          <t>16,27; 83,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,64; 80,64</t>
+          <t>9,85; 78,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,31; 164,24</t>
+          <t>48,91; 167,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 8,91</t>
+          <t>-5,82; 8,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,59</t>
+          <t>-9,72; 4,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,07; 23,72</t>
+          <t>7,8; 23,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 7,52</t>
+          <t>-8,32; 7,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 1,52</t>
+          <t>-13,11; 1,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,21; 25,7</t>
+          <t>11,74; 26,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 5,39</t>
+          <t>-5,02; 5,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,3</t>
+          <t>-9,34; 0,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,67; 22,88</t>
+          <t>12,04; 22,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 72,54</t>
+          <t>-31,97; 76,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,37; 47,52</t>
+          <t>-50,06; 39,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41,99; 201,76</t>
+          <t>37,88; 196,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 48,1</t>
+          <t>-34,68; 44,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 9,61</t>
+          <t>-55,81; 12,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,1; 166,7</t>
+          <t>46,29; 170,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 35,43</t>
+          <t>-24,21; 37,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 8,94</t>
+          <t>-45,97; 7,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60,0; 158,27</t>
+          <t>56,24; 152,01</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,06; 13,91</t>
+          <t>1,11; 14,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 12,93</t>
+          <t>-0,5; 12,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7,39; 18,63</t>
+          <t>7,35; 19,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 12,38</t>
+          <t>-1,61; 12,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 12,52</t>
+          <t>-1,57; 12,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,9; 25,97</t>
+          <t>12,87; 26,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,6</t>
+          <t>2,21; 11,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,39</t>
+          <t>1,04; 10,38</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,56; 20,6</t>
+          <t>11,45; 20,5</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,62; 135,33</t>
+          <t>6,63; 136,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 130,98</t>
+          <t>-3,9; 126,74</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45,36; 182,59</t>
+          <t>43,2; 189,48</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 86,2</t>
+          <t>-7,56; 86,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 85,12</t>
+          <t>-7,39; 85,03</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>57,39; 190,1</t>
+          <t>60,24; 183,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,45; 87,07</t>
+          <t>11,84; 85,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8,84; 79,22</t>
+          <t>4,43; 77,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>64,56; 156,01</t>
+          <t>62,5; 155,85</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,04</t>
+          <t>-2,12; 6,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,39</t>
+          <t>-2,52; 5,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,47; 21,23</t>
+          <t>11,57; 21,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,83</t>
+          <t>-4,24; 4,36</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,7</t>
+          <t>-2,39; 6,37</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,74; 56,22</t>
+          <t>17,54; 58,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,74</t>
+          <t>-2,09; 3,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,91</t>
+          <t>-1,15; 4,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16,85; 50,05</t>
+          <t>16,43; 46,18</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 45,49</t>
+          <t>-13,15; 47,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 42,82</t>
+          <t>-15,17; 41,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66,3; 160,66</t>
+          <t>67,45; 165,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 24,6</t>
+          <t>-22,37; 28,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 45,04</t>
+          <t>-12,31; 43,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>98,92; 386,36</t>
+          <t>97,66; 399,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 25,91</t>
+          <t>-11,84; 25,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 33,38</t>
+          <t>-6,42; 33,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>102,03; 346,26</t>
+          <t>98,22; 304,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,92</t>
+          <t>-2,92; 4,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,23</t>
+          <t>-6,4; 0,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 24,9</t>
+          <t>-3,9; 24,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,95</t>
+          <t>-2,63; 4,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,92</t>
+          <t>-4,95; 2,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,19; 31,05</t>
+          <t>23,15; 31,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,9</t>
+          <t>-1,53; 3,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,39</t>
+          <t>-4,34; 0,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,68; 26,03</t>
+          <t>4,98; 26,26</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 35,89</t>
+          <t>-17,1; 35,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 1,82</t>
+          <t>-37,35; 1,35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 172,94</t>
+          <t>-21,24; 169,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 39,25</t>
+          <t>-15,52; 36,37</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 21,84</t>
+          <t>-29,07; 18,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>133,72; 240,42</t>
+          <t>132,92; 242,04</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 28,11</t>
+          <t>-9,33; 25,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 2,91</t>
+          <t>-27,0; 2,9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>42,61; 179,89</t>
+          <t>34,86; 181,92</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,52</t>
+          <t>2,07; 5,46</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,54</t>
+          <t>0,14; 3,63</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8,72; 18,08</t>
+          <t>8,78; 17,98</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,21</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,34</t>
+          <t>-0,35; 3,48</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,03; 34,67</t>
+          <t>18,64; 34,33</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,41</t>
+          <t>1,87; 4,4</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,85</t>
+          <t>0,37; 2,85</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>15,72; 25,55</t>
+          <t>15,95; 25,34</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>12,08; 41,7</t>
+          <t>14,3; 43,22</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1,03; 27,47</t>
+          <t>0,89; 27,72</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>64,99; 135,45</t>
+          <t>65,13; 136,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2,69; 28,77</t>
+          <t>3,55; 29,74</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 22,62</t>
+          <t>-2,03; 23,53</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>117,58; 225,88</t>
+          <t>113,01; 222,75</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,77; 30,65</t>
+          <t>12,12; 30,69</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,22; 19,99</t>
+          <t>2,44; 19,97</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>102,76; 171,68</t>
+          <t>104,16; 173,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P37-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P37-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,78</t>
+          <t>13,54</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,13</t>
+          <t>21,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18,78</t>
+          <t>17,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 8,63</t>
+          <t>-4,03; 8,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 5,9</t>
+          <t>-5,88; 5,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 20,5</t>
+          <t>7,01; 20,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 10,29</t>
+          <t>-2,18; 10,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 10,95</t>
+          <t>-2,0; 9,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 30,09</t>
+          <t>15,12; 26,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,22</t>
+          <t>-1,36; 7,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,81</t>
+          <t>-2,49; 6,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 23,22</t>
+          <t>12,69; 21,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>199,13%</t>
+          <t>175,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139,39%</t>
+          <t>128,9%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 70,58</t>
+          <t>-22,64; 74,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 51,09</t>
+          <t>-33,1; 43,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 171,43</t>
+          <t>40,19; 177,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 113,93</t>
+          <t>-14,65; 106,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 113,61</t>
+          <t>-14,89; 103,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>115,63; 341,75</t>
+          <t>96,04; 302,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 73,21</t>
+          <t>-9,42; 65,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 58,48</t>
+          <t>-16,34; 56,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,59; 204,92</t>
+          <t>78,3; 187,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,61</t>
+          <t>17,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>18,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>17,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 12,48</t>
+          <t>3,16; 12,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,05</t>
+          <t>1,32; 9,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 22,59</t>
+          <t>11,66; 22,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 9,49</t>
+          <t>0,52; 9,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 5,23</t>
+          <t>-3,58; 5,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,43; 23,42</t>
+          <t>13,48; 22,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,19</t>
+          <t>2,95; 9,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,22</t>
+          <t>0,3; 6,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 21,39</t>
+          <t>14,25; 21,42</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160,91%</t>
+          <t>165,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>152,57%</t>
+          <t>147,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156,07%</t>
+          <t>155,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 143,73</t>
+          <t>24,41; 150,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 123,09</t>
+          <t>8,76; 120,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,47; 262,62</t>
+          <t>89,39; 269,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 92,73</t>
+          <t>3,79; 94,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 48,83</t>
+          <t>-23,86; 51,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100,29; 231,69</t>
+          <t>90,74; 221,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,11; 95,01</t>
+          <t>23,25; 93,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 63,19</t>
+          <t>2,16; 66,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107,64; 217,42</t>
+          <t>108,83; 213,83</t>
         </is>
       </c>
     </row>
@@ -1066,24 +1066,24 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>11,91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>12,34</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,28</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,71</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>12,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 11,72</t>
+          <t>-0,85; 11,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 9,85</t>
+          <t>-2,34; 9,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 17,77</t>
+          <t>6,07; 17,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 5,69</t>
+          <t>-6,46; 5,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 9,21</t>
+          <t>-3,44; 9,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 17,56</t>
+          <t>6,35; 17,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,61</t>
+          <t>-1,5; 6,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,61</t>
+          <t>-1,28; 7,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 16,2</t>
+          <t>7,76; 15,96</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 95,16</t>
+          <t>-4,48; 95,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 84,02</t>
+          <t>-13,34; 79,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,77; 142,63</t>
+          <t>31,5; 145,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 36,39</t>
+          <t>-30,41; 36,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 57,65</t>
+          <t>-16,02; 57,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 112,42</t>
+          <t>29,09; 112,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 43,91</t>
+          <t>-7,72; 45,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 50,54</t>
+          <t>-6,8; 48,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,05; 106,12</t>
+          <t>42,46; 107,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,22</t>
+          <t>17,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,27</t>
+          <t>18,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,85</t>
+          <t>17,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 11,23</t>
+          <t>0,21; 10,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 12,54</t>
+          <t>2,12; 12,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,22; 27,26</t>
+          <t>10,61; 23,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,9</t>
+          <t>1,89; 12,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,29</t>
+          <t>-1,15; 10,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 20,78</t>
+          <t>12,31; 23,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,58</t>
+          <t>2,64; 10,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,99</t>
+          <t>1,95; 10,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 21,32</t>
+          <t>13,66; 21,89</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167,52%</t>
+          <t>142,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>111,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110,3%</t>
+          <t>124,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 114,36</t>
+          <t>1,2; 115,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,75; 132,18</t>
+          <t>14,78; 128,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,59; 268,3</t>
+          <t>68,54; 237,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,59; 89,82</t>
+          <t>9,07; 90,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 73,46</t>
+          <t>-7,06; 74,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 140,04</t>
+          <t>59,32; 171,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,27; 83,75</t>
+          <t>16,2; 81,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,85; 78,13</t>
+          <t>11,31; 79,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,91; 167,69</t>
+          <t>83,34; 177,17</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,81</t>
+          <t>13,53</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,04</t>
+          <t>17,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17,69</t>
+          <t>15,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 8,64</t>
+          <t>-5,79; 8,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 4,55</t>
+          <t>-8,99; 3,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,8; 23,4</t>
+          <t>5,96; 20,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 7,14</t>
+          <t>-8,16; 7,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 1,66</t>
+          <t>-13,4; 1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,74; 26,21</t>
+          <t>10,59; 24,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,77</t>
+          <t>-4,66; 5,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 0,96</t>
+          <t>-8,76; 0,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,04; 22,45</t>
+          <t>10,69; 20,8</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101,87%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 76,15</t>
+          <t>-30,86; 78,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 39,91</t>
+          <t>-48,27; 33,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37,88; 196,19</t>
+          <t>31,28; 174,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 44,48</t>
+          <t>-34,59; 46,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,81; 12,07</t>
+          <t>-56,51; 8,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,29; 170,58</t>
+          <t>41,78; 167,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 37,62</t>
+          <t>-23,9; 36,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 7,07</t>
+          <t>-43,7; 6,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56,24; 152,01</t>
+          <t>49,92; 141,31</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,41</t>
+          <t>19,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>16,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,11; 14,49</t>
+          <t>1,9; 14,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 12,89</t>
+          <t>0,2; 12,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7,35; 19,26</t>
+          <t>7,6; 18,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 12,13</t>
+          <t>-1,97; 12,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 12,7</t>
+          <t>-1,22; 12,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,87; 26,22</t>
+          <t>11,9; 25,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,21; 11,26</t>
+          <t>2,22; 11,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,38</t>
+          <t>1,18; 10,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,45; 20,5</t>
+          <t>11,65; 20,51</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101,62%</t>
+          <t>101,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>110,42%</t>
+          <t>110,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>105,44%</t>
+          <t>105,83%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,63; 136,13</t>
+          <t>11,65; 136,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 126,74</t>
+          <t>-0,07; 113,7</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43,2; 189,48</t>
+          <t>44,52; 180,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 86,1</t>
+          <t>-10,34; 83,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 85,03</t>
+          <t>-6,12; 87,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60,24; 183,11</t>
+          <t>55,91; 178,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,84; 85,18</t>
+          <t>12,01; 82,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,43; 77,52</t>
+          <t>5,57; 80,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62,5; 155,85</t>
+          <t>65,21; 155,6</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16,54</t>
+          <t>17,67</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,48</t>
+          <t>19,23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>27,02</t>
+          <t>18,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 6,33</t>
+          <t>-2,64; 6,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,71</t>
+          <t>-2,49; 5,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,57; 21,37</t>
+          <t>12,98; 22,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,36</t>
+          <t>-4,89; 4,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 6,37</t>
+          <t>-2,12; 6,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,54; 58,3</t>
+          <t>14,37; 23,26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,84</t>
+          <t>-2,14; 3,94</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,8</t>
+          <t>-1,49; 4,7</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16,43; 46,18</t>
+          <t>15,07; 21,74</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109,81%</t>
+          <t>117,32%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>200,65%</t>
+          <t>111,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>167,37%</t>
+          <t>114,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 47,59</t>
+          <t>-14,75; 47,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 41,94</t>
+          <t>-14,69; 45,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67,45; 165,78</t>
+          <t>75,82; 172,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 28,76</t>
+          <t>-24,95; 27,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 43,29</t>
+          <t>-11,18; 44,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>97,66; 399,33</t>
+          <t>71,18; 153,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 25,96</t>
+          <t>-12,38; 27,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 33,85</t>
+          <t>-7,99; 33,07</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>98,22; 304,2</t>
+          <t>83,46; 149,76</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13,18</t>
+          <t>21,94</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,23</t>
+          <t>26,92</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19,31</t>
+          <t>24,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 4,78</t>
+          <t>-2,96; 4,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,17</t>
+          <t>-6,78; 0,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 24,52</t>
+          <t>17,65; 26,28</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,82</t>
+          <t>-2,74; 4,59</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,48</t>
+          <t>-4,57; 2,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,15; 31,5</t>
+          <t>22,26; 30,75</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,56</t>
+          <t>-1,6; 3,43</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,39</t>
+          <t>-4,76; 0,38</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,98; 26,26</t>
+          <t>21,39; 27,36</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>145,06%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>182,85%</t>
+          <t>180,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>128,7%</t>
+          <t>163,13%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 35,82</t>
+          <t>-17,56; 35,58</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 1,35</t>
+          <t>-39,6; 3,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 169,33</t>
+          <t>101,61; 202,15</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 36,37</t>
+          <t>-15,82; 34,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 18,72</t>
+          <t>-27,11; 19,33</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>132,92; 242,04</t>
+          <t>128,27; 241,23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 25,79</t>
+          <t>-9,64; 25,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 2,9</t>
+          <t>-28,31; 3,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34,86; 181,92</t>
+          <t>129,89; 200,91</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>17,04</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,19</t>
+          <t>20,14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>19,28</t>
+          <t>18,65</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,46</t>
+          <t>1,81; 5,42</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,63</t>
+          <t>0,29; 3,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8,78; 17,98</t>
+          <t>15,07; 19,08</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,6; 4,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,48</t>
+          <t>-0,58; 3,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,64; 34,33</t>
+          <t>18,28; 22,21</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,4</t>
+          <t>1,75; 4,3</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,85</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>15,95; 25,34</t>
+          <t>17,32; 20,0</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>108,98%</t>
+          <t>122,81%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>146,28%</t>
+          <t>127,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>129,58%</t>
+          <t>125,33%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14,3; 43,22</t>
+          <t>12,15; 41,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,89; 27,72</t>
+          <t>2,07; 27,78</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>65,13; 136,27</t>
+          <t>101,39; 146,65</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3,55; 29,74</t>
+          <t>3,08; 27,48</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 23,53</t>
+          <t>-3,42; 22,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>113,01; 222,75</t>
+          <t>108,86; 150,15</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,12; 30,69</t>
+          <t>11,45; 30,45</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,97</t>
+          <t>1,99; 19,85</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>104,16; 173,49</t>
+          <t>109,33; 139,98</t>
         </is>
       </c>
     </row>
